--- a/data/trans_orig/IP42B-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP42B-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3909</t>
+          <t>3907</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10970</t>
+          <t>11074</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>1507</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7725</t>
+          <t>7723</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6840</t>
+          <t>6936</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16192</t>
+          <t>16482</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>40,06%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10702</t>
+          <t>10598</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17763</t>
+          <t>17765</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11744</t>
+          <t>11746</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17953</t>
+          <t>17962</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24949</t>
+          <t>24659</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34301</t>
+          <t>34205</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,14%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1321</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7709</t>
+          <t>7030</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2807</t>
+          <t>2805</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11052</t>
+          <t>10976</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>5392</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15890</t>
+          <t>15508</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>88087</t>
+          <t>88766</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>94464</t>
+          <t>94475</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>103210</t>
+          <t>103286</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>111455</t>
+          <t>111457</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>194167</t>
+          <t>194549</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>204530</t>
+          <t>204665</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,43%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>618</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5143</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4930</t>
+          <t>4149</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7394</t>
+          <t>7577</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,6%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13426</t>
+          <t>13130</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17945</t>
+          <t>17951</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22134</t>
+          <t>22915</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>38239</t>
+          <t>38056</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>44385</t>
+          <t>44362</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,21%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>7944</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18744</t>
+          <t>18363</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6922</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17956</t>
+          <t>17396</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16854</t>
+          <t>17329</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32322</t>
+          <t>33111</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>117293</t>
+          <t>117674</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>128435</t>
+          <t>128093</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>142839</t>
+          <t>143399</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>153873</t>
+          <t>153950</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>264510</t>
+          <t>263721</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>279978</t>
+          <t>279503</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,16%</t>
         </is>
       </c>
     </row>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6986</t>
+          <t>6608</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15344</t>
+          <t>14956</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4779</t>
+          <t>4774</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12603</t>
+          <t>12377</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14065</t>
+          <t>14049</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24838</t>
+          <t>25039</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>43,26%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10569</t>
+          <t>10957</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18927</t>
+          <t>19305</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19362</t>
+          <t>19588</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27186</t>
+          <t>27191</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>61,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33040</t>
+          <t>32839</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43813</t>
+          <t>43829</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>75,73%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9446</t>
+          <t>9994</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21701</t>
+          <t>22945</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10902</t>
+          <t>11077</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23594</t>
+          <t>24262</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23623</t>
+          <t>23758</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40919</t>
+          <t>41622</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,99%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>108884</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>121139</t>
+          <t>120591</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>106105</t>
+          <t>105437</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>118797</t>
+          <t>118622</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>219365</t>
+          <t>218662</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>236661</t>
+          <t>236526</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,87%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>678</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5644</t>
+          <t>5635</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4748</t>
+          <t>5083</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1524</t>
+          <t>1492</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8090</t>
+          <t>8071</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,61%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16565</t>
+          <t>16574</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21570</t>
+          <t>21531</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21622</t>
+          <t>21287</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>40490</t>
+          <t>40509</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>47056</t>
+          <t>47088</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,93%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20048</t>
+          <t>21221</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36695</t>
+          <t>37511</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19076</t>
+          <t>19449</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35275</t>
+          <t>35299</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44175</t>
+          <t>43786</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66638</t>
+          <t>66645</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>142012</t>
+          <t>141196</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>158659</t>
+          <t>157486</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>152759</t>
+          <t>152735</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>168958</t>
+          <t>168585</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>300103</t>
+          <t>300096</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>322566</t>
+          <t>322955</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>88,06%</t>
         </is>
       </c>
     </row>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7005</t>
+          <t>7071</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1322</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6719</t>
+          <t>7269</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3359</t>
+          <t>3501</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11714</t>
+          <t>12009</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,98%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21214</t>
+          <t>21148</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26972</t>
+          <t>27017</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22313</t>
+          <t>21763</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27710</t>
+          <t>27726</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45537</t>
+          <t>45242</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53892</t>
+          <t>53750</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>93,88%</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6732</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17443</t>
+          <t>16973</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6781</t>
+          <t>7084</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17562</t>
+          <t>18026</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15932</t>
+          <t>15729</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30182</t>
+          <t>30589</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>123628</t>
+          <t>124098</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>134339</t>
+          <t>133947</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>152904</t>
+          <t>152440</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>163685</t>
+          <t>163382</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>281356</t>
+          <t>280949</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>295606</t>
+          <t>295809</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,95%</t>
         </is>
       </c>
     </row>
@@ -4624,12 +4624,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>708</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6244</t>
+          <t>6061</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>721</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6276</t>
+          <t>6273</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2743</t>
+          <t>2562</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10802</t>
+          <t>9751</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -4737,12 +4737,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26539</t>
+          <t>26722</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32022</t>
+          <t>32075</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28761</t>
+          <t>28764</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34315</t>
+          <t>34316</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>57018</t>
+          <t>58069</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>65077</t>
+          <t>65258</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,22%</t>
         </is>
       </c>
     </row>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11426</t>
+          <t>12180</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24573</t>
+          <t>24540</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11986</t>
+          <t>11510</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24817</t>
+          <t>25294</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26344</t>
+          <t>26230</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45078</t>
+          <t>45458</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>177500</t>
+          <t>177533</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>190647</t>
+          <t>189893</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>209718</t>
+          <t>209241</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>222549</t>
+          <t>223025</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>391530</t>
+          <t>391150</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>410264</t>
+          <t>410378</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,99%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP42B-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP42B-Estudios-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1980</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7742</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>21,59%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>10,17%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>39,77%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>6936</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3907</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11074</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3878</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>10752</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>32,01%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>18,03%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>51,1%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4204</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1507</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7723</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>21,59%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6936</t>
+          <t>6736</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16482</t>
+          <t>16298</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>39,62%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>15265</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11727</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>17489</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>78,41%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>60,23%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>89,83%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>14736</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>10598</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>17765</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>10920</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>17794</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>67,99%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>48,9%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>81,97%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>15265</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>11746</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>17962</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>78,41%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>50,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24659</t>
+          <t>24843</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34205</t>
+          <t>34405</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,63%</t>
         </is>
       </c>
     </row>
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>19469</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>19469</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>19469</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>21672</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>21672</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>21672</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>19469</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>19469</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>19469</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6193</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2764</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11000</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,42%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,63%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>3449</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1321</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7030</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1347</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7728</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>3,6%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,34%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>6193</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2805</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>10976</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>5,42%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5392</t>
+          <t>5595</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15508</t>
+          <t>15733</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>108069</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>103262</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>111498</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,58%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>90,37%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,58%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>139</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>92347</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>88766</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>94475</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>88068</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>94449</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>96,4%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>92,66%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,62%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>108069</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>103286</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>111457</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>94,58%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>194549</t>
+          <t>194324</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>204665</t>
+          <t>204462</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>114262</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>114262</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>114262</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>95796</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>95796</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>95796</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>114262</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>114262</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>114262</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1367</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5243</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,05%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>19,37%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2111</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>618</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5439</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5348</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>11,37%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>3,33%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>29,29%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1367</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4149</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,05%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7577</t>
+          <t>7627</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,71%</t>
         </is>
       </c>
     </row>
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>25697</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>21821</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>27064</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,95%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>80,63%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>16458</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>13130</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>13221</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>17951</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>88,63%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>70,71%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>71,2%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>96,67%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>25697</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>22915</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>27064</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,95%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>84,67%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>63</t>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>38056</t>
+          <t>38006</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>44362</t>
+          <t>44353</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,19%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>27064</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>27064</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>27064</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>18569</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>18569</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>18569</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>27064</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>27064</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>27064</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11764</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7026</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>17578</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7,32%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,37%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10,93%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>12496</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>7944</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>18363</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>7509</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>18963</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>9,19%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5,84%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>13,5%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>11764</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>6845</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>17396</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17329</t>
+          <t>17297</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33111</t>
+          <t>31965</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>149031</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>143217</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>153769</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>92,68%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>89,07%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>95,63%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>123541</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>117674</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>128093</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>117074</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>128528</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>90,81%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>86,5%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>94,16%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>149031</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>143399</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>153950</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>92,68%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>263721</t>
+          <t>264867</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>279503</t>
+          <t>279535</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,17%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>160795</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>160795</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>160795</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>136037</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>136037</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>136037</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>160795</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>160795</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>160795</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2157,7 +2157,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2325,72 +2325,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8169</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4823</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12512</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>25,56%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>15,09%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>39,14%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>10909</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6608</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>14956</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>6878</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>15236</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>42,1%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>25,5%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>57,71%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>8169</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>4774</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>12377</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>25,56%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14049</t>
+          <t>13719</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25039</t>
+          <t>25071</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,32%</t>
         </is>
       </c>
     </row>
@@ -2438,72 +2438,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>23796</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>19453</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>27142</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>74,44%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>60,86%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>84,91%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>15004</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>10957</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>19305</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>10677</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>19035</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>57,9%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>42,29%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>74,5%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>23796</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>19588</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>27191</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>74,44%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32839</t>
+          <t>32807</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43829</t>
+          <t>44159</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>76,3%</t>
         </is>
       </c>
     </row>
@@ -2551,57 +2551,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>31965</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>31965</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>31965</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>25913</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>25913</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>25913</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>31965</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>31965</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>31965</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2668,72 +2668,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>16717</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>11079</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>23631</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>12,89%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>8,54%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>18,22%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>14942</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>9994</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>22945</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>9802</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>22387</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>11,44%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>7,65%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>17,57%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>16717</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>11077</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>24262</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>12,89%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23758</t>
+          <t>23764</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41622</t>
+          <t>41913</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,1%</t>
         </is>
       </c>
     </row>
@@ -2781,72 +2781,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>112982</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>106068</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>118620</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>87,11%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>81,78%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>91,46%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>115643</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>107640</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>120591</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>108198</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>120783</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>88,56%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>82,43%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>92,35%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>112982</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>105437</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>118622</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>87,11%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>218662</t>
+          <t>218371</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>236526</t>
+          <t>236520</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -2894,57 +2894,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>129699</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>129699</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>129699</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>130585</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>130585</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>130585</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>129699</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>129699</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>129699</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3011,72 +3011,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1507</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4228</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,72%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>16,03%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2373</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>678</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5635</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5265</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>10,68%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>25,37%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1507</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5083</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,72%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1492</t>
+          <t>1747</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8071</t>
+          <t>8027</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,52%</t>
         </is>
       </c>
     </row>
@@ -3124,72 +3124,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>24863</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>22142</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>26370</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,28%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>83,97%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>19836</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>16574</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>21531</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>16944</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>21586</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>89,32%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>74,63%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,95%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>24863</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>21287</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>26370</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,28%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>40509</t>
+          <t>40553</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>47088</t>
+          <t>46833</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,4%</t>
         </is>
       </c>
     </row>
@@ -3237,57 +3237,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>26370</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>26370</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>26370</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>22209</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>22209</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>22209</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>26370</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>26370</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>26370</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3354,72 +3354,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>26394</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>18970</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>35036</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>14,04%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10,09%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>18,63%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>28224</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>21221</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>37511</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>20630</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>36151</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>15,79%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>11,87%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>20,99%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>26394</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>19449</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>35299</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>14,04%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43786</t>
+          <t>43936</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66645</t>
+          <t>65513</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>17,86%</t>
         </is>
       </c>
     </row>
@@ -3467,72 +3467,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>161640</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>152998</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>169064</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>85,96%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>81,37%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>89,91%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>150483</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>141196</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>157486</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>142556</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>158077</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>84,21%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>79,01%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>88,13%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>161640</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>152735</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>168585</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>85,96%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>300096</t>
+          <t>301228</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>322955</t>
+          <t>322805</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,02%</t>
         </is>
       </c>
     </row>
@@ -3580,57 +3580,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>188034</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>188034</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>188034</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>178707</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>178707</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>178707</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>188034</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>188034</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>188034</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3760,7 +3760,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3933,67 +3933,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>3439</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1317</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6895</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>11,84%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4,54%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>23,75%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>3416</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1202</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7071</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1184</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6679</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>12,11%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,26%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>25,06%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3439</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1306</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7269</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>11,84%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3501</t>
+          <t>3454</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12009</t>
+          <t>11711</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,46%</t>
         </is>
       </c>
     </row>
@@ -4046,67 +4046,67 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>25593</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>22137</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>27715</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>88,16%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>76,25%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>95,46%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>24803</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>21148</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>27017</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>21540</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>27035</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>87,89%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>74,94%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>95,74%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>25593</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>21763</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>27726</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>88,16%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45242</t>
+          <t>45540</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53750</t>
+          <t>53797</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,97%</t>
         </is>
       </c>
     </row>
@@ -4159,52 +4159,52 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>29032</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>29032</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>29032</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>28219</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>28219</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>28219</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>29032</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>29032</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>29032</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4271,72 +4271,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11438</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6396</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>17395</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6,71%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,75%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10,2%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>11030</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>7124</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>16973</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>6788</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>16840</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>7,82%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5,05%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>12,03%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>11438</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>7084</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>18026</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>6,71%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15729</t>
+          <t>15372</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30589</t>
+          <t>30919</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -4384,72 +4384,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>159028</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>153071</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>164070</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>93,29%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>89,8%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,25%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>199</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>130041</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>124098</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>133947</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>124231</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>134283</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>92,18%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>87,97%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>94,95%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>159028</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>152440</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>163382</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>93,29%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>280949</t>
+          <t>280619</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>295809</t>
+          <t>296166</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,07%</t>
         </is>
       </c>
     </row>
@@ -4497,57 +4497,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>170466</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>170466</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>170466</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>141071</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>141071</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>141071</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>170466</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>170466</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>170466</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4619,67 +4619,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>2690</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>724</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6042</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7,68%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>17,25%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>2584</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>708</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6061</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>731</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6127</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>7,88%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>18,49%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2690</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>721</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6273</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>7,68%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2562</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9751</t>
+          <t>9593</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,14%</t>
         </is>
       </c>
     </row>
@@ -4732,67 +4732,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>32347</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>28995</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>34313</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>92,32%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>82,75%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,93%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>30199</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>26722</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>32075</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>26656</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>32052</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>92,12%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>81,51%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,84%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>32347</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>28764</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>34316</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>92,32%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>58069</t>
+          <t>58227</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>65258</t>
+          <t>65411</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,45%</t>
         </is>
       </c>
     </row>
@@ -4845,52 +4845,52 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>35037</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>35037</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>35037</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>32783</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>32783</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>32783</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>35037</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>35037</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>35037</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4957,72 +4957,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>17567</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>11284</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>24965</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7,49%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,81%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10,64%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>17029</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>12180</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>24540</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>11500</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>24287</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>8,43%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,03%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>12,14%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>17567</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>11510</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>25294</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>7,49%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26230</t>
+          <t>26016</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45458</t>
+          <t>43951</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -5070,72 +5070,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>216968</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>209570</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>223251</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>92,51%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>89,36%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>95,19%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>282</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>185044</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>177533</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>189893</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>177786</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>190573</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>91,57%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>87,86%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>93,97%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>216968</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>209241</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>223025</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>92,51%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>391150</t>
+          <t>392657</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>410378</t>
+          <t>410592</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,04%</t>
         </is>
       </c>
     </row>
@@ -5183,57 +5183,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>234535</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>234535</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>234535</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>308</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>202073</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>202073</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>202073</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>335</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>234535</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>234535</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>234535</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
